--- a/Pitrudosha and Career.xlsx
+++ b/Pitrudosha and Career.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aksha\Desktop\Kareer Studio\Astrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C98E85-B314-412D-8FAB-15DC7447A0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D5C558-3D91-4619-8C0D-0B1897D9A24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{46B42B48-BBD9-4A5E-8CE9-B2058DC6CFDE}"/>
   </bookViews>
